--- a/TRADING-SYSTEM/05-EXCEL/stat-arb-journal.xlsx
+++ b/TRADING-SYSTEM/05-EXCEL/stat-arb-journal.xlsx
@@ -10,6 +10,7 @@
     <sheet name="Калькулятор" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Журнал" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Сводка" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Задачи" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -149,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -184,6 +185,18 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -3673,4 +3686,839 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="80" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="5" customWidth="1" min="5" max="5"/>
+    <col width="48" customWidth="1" min="6" max="6"/>
+    <col hidden="1" width="15" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ЗАДАЧИ — триангулярный стат-арб (детсад → практик)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Вписывай жёлтый «Твой ответ» → ✓ загорится само (допуск ±1%). Правильный ответ скрыт в столбце G — разверни, только если застрял.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="20" t="inlineStr">
+        <is>
+          <t>№</t>
+        </is>
+      </c>
+      <c r="B3" s="20" t="inlineStr">
+        <is>
+          <t>Уровень</t>
+        </is>
+      </c>
+      <c r="C3" s="20" t="inlineStr">
+        <is>
+          <t>Вопрос</t>
+        </is>
+      </c>
+      <c r="D3" s="20" t="inlineStr">
+        <is>
+          <t>Твой ответ</t>
+        </is>
+      </c>
+      <c r="E3" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F3" s="20" t="inlineStr">
+        <is>
+          <t>Подсказка / формула</t>
+        </is>
+      </c>
+      <c r="G3" s="20" t="inlineStr">
+        <is>
+          <t>Ответ</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>🧸 Детсад</t>
+        </is>
+      </c>
+      <c r="C4" s="29" t="inlineStr">
+        <is>
+          <t>1 EUR = 1.08 USD. Сколько USD за 50 EUR?</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="28">
+        <f>IF(D4="","",IF(ABS(D4-G4)&lt;=ABS(G4)*0.01+0.0001,"✓","✗"))</f>
+        <v/>
+      </c>
+      <c r="F4" s="30" t="inlineStr">
+        <is>
+          <t>умножь курс на количество</t>
+        </is>
+      </c>
+      <c r="G4" s="13">
+        <f>1.08*50</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>🧸 Детсад</t>
+        </is>
+      </c>
+      <c r="C5" s="29" t="inlineStr">
+        <is>
+          <t>1 USD = 150 JPY. Сколько JPY за 100 USD?</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="n"/>
+      <c r="E5" s="28">
+        <f>IF(D5="","",IF(ABS(D5-G5)&lt;=ABS(G5)*0.01+0.0001,"✓","✗"))</f>
+        <v/>
+      </c>
+      <c r="F5" s="30" t="inlineStr">
+        <is>
+          <t>умножь</t>
+        </is>
+      </c>
+      <c r="G5" s="13">
+        <f>150*100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="28" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>🧸 Детсад</t>
+        </is>
+      </c>
+      <c r="C6" s="29" t="inlineStr">
+        <is>
+          <t>1 EUR = 1.08 USD и 1 USD = 150 JPY. Сколько JPY за 1 EUR через доллар?</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="n"/>
+      <c r="E6" s="28">
+        <f>IF(D6="","",IF(ABS(D6-G6)&lt;=ABS(G6)*0.01+0.0001,"✓","✗"))</f>
+        <v/>
+      </c>
+      <c r="F6" s="30" t="inlineStr">
+        <is>
+          <t>перемножь два курса = синтетический EURJPY</t>
+        </is>
+      </c>
+      <c r="G6" s="13">
+        <f>1.08*150</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="28" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>🧸 Детсад</t>
+        </is>
+      </c>
+      <c r="C7" s="29" t="inlineStr">
+        <is>
+          <t>У тебя 16 200 JPY, курс EURJPY = 162. Сколько это EUR?</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="n"/>
+      <c r="E7" s="28">
+        <f>IF(D7="","",IF(ABS(D7-G7)&lt;=ABS(G7)*0.01+0.0001,"✓","✗"))</f>
+        <v/>
+      </c>
+      <c r="F7" s="30" t="inlineStr">
+        <is>
+          <t>дели сумму на курс</t>
+        </is>
+      </c>
+      <c r="G7" s="13">
+        <f>16200/162</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="28" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>🧸 Детсад</t>
+        </is>
+      </c>
+      <c r="C8" s="29" t="inlineStr">
+        <is>
+          <t>Старт 100 EUR → доллары (×1.08) → йены (×150) → назад в EUR по EURJPY=162.30. Сколько EUR в конце? (&lt;100 = потерял)</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="n"/>
+      <c r="E8" s="28">
+        <f>IF(D8="","",IF(ABS(D8-G8)&lt;=ABS(G8)*0.01+0.0001,"✓","✗"))</f>
+        <v/>
+      </c>
+      <c r="F8" s="30" t="inlineStr">
+        <is>
+          <t>умножай при продаже, дели при выкупе</t>
+        </is>
+      </c>
+      <c r="G8" s="13">
+        <f>100*1.08*150/162.30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="28" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>🎒 Школа</t>
+        </is>
+      </c>
+      <c r="C9" s="29" t="inlineStr">
+        <is>
+          <t>Синтетика EURJPY = 1.08×150. Прямая котировка = 162.30. Гэп в пунктах (йенах)?</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="n"/>
+      <c r="E9" s="28">
+        <f>IF(D9="","",IF(ABS(D9-G9)&lt;=ABS(G9)*0.01+0.0001,"✓","✗"))</f>
+        <v/>
+      </c>
+      <c r="F9" s="30" t="inlineStr">
+        <is>
+          <t>прямая − синтетика</t>
+        </is>
+      </c>
+      <c r="G9" s="13">
+        <f>162.30-1.08*150</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="28" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>🎒 Школа</t>
+        </is>
+      </c>
+      <c r="C10" s="29" t="inlineStr">
+        <is>
+          <t>Тот же гэп в процентах от синтетики?</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="n"/>
+      <c r="E10" s="28">
+        <f>IF(D10="","",IF(ABS(D10-G10)&lt;=ABS(G10)*0.01+0.0001,"✓","✗"))</f>
+        <v/>
+      </c>
+      <c r="F10" s="30" t="inlineStr">
+        <is>
+          <t>(прямая/синт − 1)×100</t>
+        </is>
+      </c>
+      <c r="G10" s="13">
+        <f>(162.30/(1.08*150)-1)*100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="28" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>🎒 Школа</t>
+        </is>
+      </c>
+      <c r="C11" s="29" t="inlineStr">
+        <is>
+          <t>EURJPY с 2 знаками, 1 пункт = 0.01. Гэп 0.30 = сколько пунктов?</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="n"/>
+      <c r="E11" s="28">
+        <f>IF(D11="","",IF(ABS(D11-G11)&lt;=ABS(G11)*0.01+0.0001,"✓","✗"))</f>
+        <v/>
+      </c>
+      <c r="F11" s="30" t="inlineStr">
+        <is>
+          <t>дели гэп на размер пункта</t>
+        </is>
+      </c>
+      <c r="G11" s="13">
+        <f>0.30/0.01</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="28" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>🎒 Школа</t>
+        </is>
+      </c>
+      <c r="C12" s="29" t="inlineStr">
+        <is>
+          <t>Круг проходит 3 ноги, каждая 0.04% туда-обратно. Сколько % съест весь круг?</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="n"/>
+      <c r="E12" s="28">
+        <f>IF(D12="","",IF(ABS(D12-G12)&lt;=ABS(G12)*0.01+0.0001,"✓","✗"))</f>
+        <v/>
+      </c>
+      <c r="F12" s="30" t="inlineStr">
+        <is>
+          <t>сложи издержки трёх ног</t>
+        </is>
+      </c>
+      <c r="G12" s="13">
+        <f>3*0.04</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="28" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>🎒 Школа</t>
+        </is>
+      </c>
+      <c r="C13" s="29" t="inlineStr">
+        <is>
+          <t>Край круга 0.185% против издержек 0.12%. Сколько нетто остаётся, %?</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="n"/>
+      <c r="E13" s="28">
+        <f>IF(D13="","",IF(ABS(D13-G13)&lt;=ABS(G13)*0.01+0.0001,"✓","✗"))</f>
+        <v/>
+      </c>
+      <c r="F13" s="30" t="inlineStr">
+        <is>
+          <t>край − издержки; &gt;0 = живой</t>
+        </is>
+      </c>
+      <c r="G13" s="13">
+        <f>0.185-0.12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="28" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>🎒 Школа</t>
+        </is>
+      </c>
+      <c r="C14" s="29" t="inlineStr">
+        <is>
+          <t>Лог-остаток x = ln(162.30) − ln(1.08) − ln(150). Посчитай.</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="28">
+        <f>IF(D14="","",IF(ABS(D14-G14)&lt;=ABS(G14)*0.01+0.0001,"✓","✗"))</f>
+        <v/>
+      </c>
+      <c r="F14" s="30" t="inlineStr">
+        <is>
+          <t>натуральный лог, знаки (+,−,−)</t>
+        </is>
+      </c>
+      <c r="G14" s="13">
+        <f>LN(162.30)-LN(1.08)-LN(150)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="28" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="13" t="inlineStr">
+        <is>
+          <t>🎓 Универ</t>
+        </is>
+      </c>
+      <c r="C15" s="29" t="inlineStr">
+        <is>
+          <t>Коинтегрирующий вектор на (ln EURJPY, ln EURUSD, ln USDJPY)? Три числа.</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="31" t="inlineStr">
+        <is>
+          <t>устно</t>
+        </is>
+      </c>
+      <c r="F15" s="30" t="inlineStr">
+        <is>
+          <t>из тождества c=e·j → ln c − ln e − ln j = 0</t>
+        </is>
+      </c>
+      <c r="G15" s="13" t="inlineStr">
+        <is>
+          <t>(1; -1; -1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="28" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t>🎓 Универ</t>
+        </is>
+      </c>
+      <c r="C16" s="29" t="inlineStr">
+        <is>
+          <t>Лонг 100 000 EUR ноционала в EURJPY. Какой USD-ноционал в EURUSD-ноге обнуляет EUR? (×1.08)</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="28">
+        <f>IF(D16="","",IF(ABS(D16-G16)&lt;=ABS(G16)*0.01+0.0001,"✓","✗"))</f>
+        <v/>
+      </c>
+      <c r="F16" s="30" t="inlineStr">
+        <is>
+          <t>EUR-ноционал × курс EURUSD</t>
+        </is>
+      </c>
+      <c r="G16" s="13">
+        <f>100000*1.08</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="28" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="13" t="inlineStr">
+        <is>
+          <t>🎓 Универ</t>
+        </is>
+      </c>
+      <c r="C17" s="29" t="inlineStr">
+        <is>
+          <t>Та же корзина: JPY-ноционал в USDJPY-ноге? (EUR × 1.08 × 150)</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="n"/>
+      <c r="E17" s="28">
+        <f>IF(D17="","",IF(ABS(D17-G17)&lt;=ABS(G17)*0.01+0.0001,"✓","✗"))</f>
+        <v/>
+      </c>
+      <c r="F17" s="30" t="inlineStr">
+        <is>
+          <t>прогон по цепочке валют 1 : e : e·j</t>
+        </is>
+      </c>
+      <c r="G17" s="13">
+        <f>100000*1.08*150</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="28" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="13" t="inlineStr">
+        <is>
+          <t>🎓 Универ</t>
+        </is>
+      </c>
+      <c r="C18" s="29" t="inlineStr">
+        <is>
+          <t>Остаток: μ=0, σ=0.0003 (лог), текущий x=0.0008. z-score?</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="n"/>
+      <c r="E18" s="28">
+        <f>IF(D18="","",IF(ABS(D18-G18)&lt;=ABS(G18)*0.01+0.0001,"✓","✗"))</f>
+        <v/>
+      </c>
+      <c r="F18" s="30" t="inlineStr">
+        <is>
+          <t>(x − μ) / σ</t>
+        </is>
+      </c>
+      <c r="G18" s="13">
+        <f>(0.0008-0)/0.0003</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="28" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="13" t="inlineStr">
+        <is>
+          <t>🎓 Универ</t>
+        </is>
+      </c>
+      <c r="C19" s="29" t="inlineStr">
+        <is>
+          <t>Порог входа z=2, текущий z=2.667 — сигнал есть? (1=да, 0=нет)</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="n"/>
+      <c r="E19" s="28">
+        <f>IF(D19="","",IF(ABS(D19-G19)&lt;=ABS(G19)*0.01+0.0001,"✓","✗"))</f>
+        <v/>
+      </c>
+      <c r="F19" s="30" t="inlineStr">
+        <is>
+          <t>сравни |z| с порогом</t>
+        </is>
+      </c>
+      <c r="G19" s="13">
+        <f>IF(2.667&gt;=2,1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="28" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" s="13" t="inlineStr">
+        <is>
+          <t>🎓 Универ</t>
+        </is>
+      </c>
+      <c r="C20" s="29" t="inlineStr">
+        <is>
+          <t>OU-процесс, скорость возврата κ=0.5 в минуту. Полупериод возврата (мин)?</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="n"/>
+      <c r="E20" s="28">
+        <f>IF(D20="","",IF(ABS(D20-G20)&lt;=ABS(G20)*0.01+0.0001,"✓","✗"))</f>
+        <v/>
+      </c>
+      <c r="F20" s="30" t="inlineStr">
+        <is>
+          <t>half-life = ln2 / κ</t>
+        </is>
+      </c>
+      <c r="G20" s="13">
+        <f>LN(2)/0.5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="28" t="n">
+        <v>18</v>
+      </c>
+      <c r="B21" s="13" t="inlineStr">
+        <is>
+          <t>🎓 Универ</t>
+        </is>
+      </c>
+      <c r="C21" s="29" t="inlineStr">
+        <is>
+          <t>Лог-остаток обратно в %: x=0.001849 → (e^x − 1)×100 = ?</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="n"/>
+      <c r="E21" s="28">
+        <f>IF(D21="","",IF(ABS(D21-G21)&lt;=ABS(G21)*0.01+0.0001,"✓","✗"))</f>
+        <v/>
+      </c>
+      <c r="F21" s="30" t="inlineStr">
+        <is>
+          <t>exp(x) − 1, ×100</t>
+        </is>
+      </c>
+      <c r="G21" s="13">
+        <f>(EXP(0.001849)-1)*100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="28" t="n">
+        <v>19</v>
+      </c>
+      <c r="B22" s="13" t="inlineStr">
+        <is>
+          <t>🎓 Универ</t>
+        </is>
+      </c>
+      <c r="C22" s="29" t="inlineStr">
+        <is>
+          <t>Почему σ остатка (0.0003) ≪ σ ноги (~0.01)? Словами.</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="n"/>
+      <c r="E22" s="31" t="inlineStr">
+        <is>
+          <t>устно</t>
+        </is>
+      </c>
+      <c r="F22" s="30" t="inlineStr">
+        <is>
+          <t>: Var(a−b−c) при корреляции →1 стремится к 0</t>
+        </is>
+      </c>
+      <c r="G22" s="13" t="inlineStr">
+        <is>
+          <t>ноги коинтегрированы (ходят вместе) → дисперсии в комбинации (1,−1,−1) почти гасятся</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="30" customHeight="1">
+      <c r="A23" s="28" t="n">
+        <v>20</v>
+      </c>
+      <c r="B23" s="13" t="inlineStr">
+        <is>
+          <t>💼 Практик</t>
+        </is>
+      </c>
+      <c r="C23" s="29" t="inlineStr">
+        <is>
+          <t>Круг по стакану: продаёшь EUR по EURUSD bid 1.0800 → USD по USDJPY bid 150.00 → выкуп EUR по EURJPY ask 162.40. Сколько EUR на 1 EUR?</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="n"/>
+      <c r="E23" s="28">
+        <f>IF(D23="","",IF(ABS(D23-G23)&lt;=ABS(G23)*0.01+0.0001,"✓","✗"))</f>
+        <v/>
+      </c>
+      <c r="F23" s="30" t="inlineStr">
+        <is>
+          <t>перемножь исполняемые курсы; выкуп = деление на ask</t>
+        </is>
+      </c>
+      <c r="G23" s="13">
+        <f>1.0800*150.00/162.40</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="30" customHeight="1">
+      <c r="A24" s="28" t="n">
+        <v>21</v>
+      </c>
+      <c r="B24" s="13" t="inlineStr">
+        <is>
+          <t>💼 Практик</t>
+        </is>
+      </c>
+      <c r="C24" s="29" t="inlineStr">
+        <is>
+          <t>Тот круг — сколько потерял, %?</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="n"/>
+      <c r="E24" s="28">
+        <f>IF(D24="","",IF(ABS(D24-G24)&lt;=ABS(G24)*0.01+0.0001,"✓","✗"))</f>
+        <v/>
+      </c>
+      <c r="F24" s="30" t="inlineStr">
+        <is>
+          <t>(результат − 1)×100; минус = убыток (издержки съели)</t>
+        </is>
+      </c>
+      <c r="G24" s="13">
+        <f>(1.0800*150.00/162.40-1)*100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="30" customHeight="1">
+      <c r="A25" s="28" t="n">
+        <v>22</v>
+      </c>
+      <c r="B25" s="13" t="inlineStr">
+        <is>
+          <t>💼 Практик</t>
+        </is>
+      </c>
+      <c r="C25" s="29" t="inlineStr">
+        <is>
+          <t>Кросс-венью: EURJPY на площадке A = 162.30, на B = 162.10. Базис в пунктах?</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="n"/>
+      <c r="E25" s="28">
+        <f>IF(D25="","",IF(ABS(D25-G25)&lt;=ABS(G25)*0.01+0.0001,"✓","✗"))</f>
+        <v/>
+      </c>
+      <c r="F25" s="30" t="inlineStr">
+        <is>
+          <t>разница цены ОДНОЙ пары на двух площадках — вот где край живёт</t>
+        </is>
+      </c>
+      <c r="G25" s="13">
+        <f>162.30-162.10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="28" t="n">
+        <v>23</v>
+      </c>
+      <c r="B26" s="13" t="inlineStr">
+        <is>
+          <t>💼 Практик</t>
+        </is>
+      </c>
+      <c r="C26" s="29" t="inlineStr">
+        <is>
+          <t>CIP-форвард EURUSD на год: спот 1.0800, r_USD=5%, r_EUR=3%. Форвард = спот×(1+r_USD)/(1+r_EUR).</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="n"/>
+      <c r="E26" s="28">
+        <f>IF(D26="","",IF(ABS(D26-G26)&lt;=ABS(G26)*0.01+0.0001,"✓","✗"))</f>
+        <v/>
+      </c>
+      <c r="F26" s="30" t="inlineStr">
+        <is>
+          <t>паритет покрытых процентных ставок</t>
+        </is>
+      </c>
+      <c r="G26" s="13">
+        <f>1.0800*(1+0.05)/(1+0.03)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="28" t="n">
+        <v>24</v>
+      </c>
+      <c r="B27" s="13" t="inlineStr">
+        <is>
+          <t>💼 Практик</t>
+        </is>
+      </c>
+      <c r="C27" s="29" t="inlineStr">
+        <is>
+          <t>Рыночный форвард = 1.0980. Кросс-валютный базис = рынок − CIP-форвард. Посчитай.</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="n"/>
+      <c r="E27" s="28">
+        <f>IF(D27="","",IF(ABS(D27-G27)&lt;=ABS(G27)*0.01+0.0001,"✓","✗"))</f>
+        <v/>
+      </c>
+      <c r="F27" s="30" t="inlineStr">
+        <is>
+          <t>market − CIP = xccy basis, реальный край банковских десков</t>
+        </is>
+      </c>
+      <c r="G27" s="13">
+        <f>1.0980-1.0800*(1+0.05)/(1+0.03)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="30" customHeight="1">
+      <c r="A28" s="28" t="n">
+        <v>25</v>
+      </c>
+      <c r="B28" s="13" t="inlineStr">
+        <is>
+          <t>💼 Практик</t>
+        </is>
+      </c>
+      <c r="C28" s="29" t="inlineStr">
+        <is>
+          <t>Цикл 4 курсов: EUR→USD 1.08, USD→JPY 150, JPY→GBP 0.0053, GBP→EUR 1.16. Произведение по кругу?</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="n"/>
+      <c r="E28" s="28">
+        <f>IF(D28="","",IF(ABS(D28-G28)&lt;=ABS(G28)*0.01+0.0001,"✓","✗"))</f>
+        <v/>
+      </c>
+      <c r="F28" s="30" t="inlineStr">
+        <is>
+          <t>произведение по замкнутому циклу; ≠1 = арбитраж (&gt;1 прибыль). Это Bellman–Ford</t>
+        </is>
+      </c>
+      <c r="G28" s="13">
+        <f>1.08*150*0.0053*1.16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" ht="30" customHeight="1">
+      <c r="A29" s="28" t="n">
+        <v>26</v>
+      </c>
+      <c r="B29" s="13" t="inlineStr">
+        <is>
+          <t>💼 Практик</t>
+        </is>
+      </c>
+      <c r="C29" s="29" t="inlineStr">
+        <is>
+          <t>Годовой Шарп: край 2 б.п./цикл, σ 3 б.п., 50 циклов/день, 252 дня. Sharpe = (2/3)×√(50×252).</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="n"/>
+      <c r="E29" s="28">
+        <f>IF(D29="","",IF(ABS(D29-G29)&lt;=ABS(G29)*0.01+0.0001,"✓","✗"))</f>
+        <v/>
+      </c>
+      <c r="F29" s="30" t="inlineStr">
+        <is>
+          <t>Sharpe = средн/σ × √(сделок в год). Заоблачный → оттого за край дерётся HFT; в ликвиде он ≈0 после издержек</t>
+        </is>
+      </c>
+      <c r="G29" s="13">
+        <f>(2/3)*SQRT(50*252)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>